--- a/CRMTest/src/main/java/com/crm/qa/testdata/TestData.xlsx
+++ b/CRMTest/src/main/java/com/crm/qa/testdata/TestData.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7620"/>
+    <workbookView windowWidth="20490" windowHeight="7620" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Contact" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Task" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>firstname</t>
   </si>
@@ -71,6 +71,72 @@
   </si>
   <si>
     <t>C:\Users\admin\OneDrive\Desktop\Vikram\SampleFish.jpg</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>AssignedTo</t>
+  </si>
+  <si>
+    <t>month_year</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Completion</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Pirority</t>
+  </si>
+  <si>
+    <t>Identifier</t>
+  </si>
+  <si>
+    <t>Mr</t>
+  </si>
+  <si>
+    <t>vikram s</t>
+  </si>
+  <si>
+    <t>April 2023</t>
+  </si>
+  <si>
+    <t>ncs soft solutions</t>
+  </si>
+  <si>
+    <t>Enquiring</t>
+  </si>
+  <si>
+    <t>Complaint</t>
+  </si>
+  <si>
+    <t>Qwerty26</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>top notch</t>
   </si>
 </sst>
 </file>
@@ -244,7 +310,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -259,6 +325,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -444,12 +516,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -574,7 +661,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -586,120 +673,125 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -714,7 +806,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1059,19 +1151,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1119,9 +1211,116 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <sheetData/>
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2"/>
+  <cols>
+    <col min="2" max="2" width="11.8571428571429" customWidth="1"/>
+    <col min="3" max="3" width="12.5714285714286" customWidth="1"/>
+    <col min="6" max="6" width="18.7142857142857" customWidth="1"/>
+    <col min="7" max="7" width="12.2857142857143" customWidth="1"/>
+    <col min="10" max="10" width="11.7142857142857"/>
+    <col min="11" max="11" width="11.8571428571429" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="3">
+        <v>18</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.572916666666667</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="3">
+        <v>77</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="3">
+        <v>9952994400</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
